--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261023.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261023.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.65</v>
+        <v>0.6566115702479338</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,13 +716,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.022099173553719</v>
+        <v>0.02871074380165282</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>おおむね予定どおり 28件／前倒し 12件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
+          <t>おおむね予定どおり 27件／前倒し 13件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -5208,47 +5208,47 @@
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E37" s="19" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="G37" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H37" s="30" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="I37" s="30" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J37" s="30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K37" s="19" t="n">
         <v>3</v>
@@ -5260,29 +5260,29 @@
       </c>
       <c r="M37" s="18" t="inlineStr">
         <is>
-          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
+          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>回収票の点検・ナンバリング・データ入力</t>
         </is>
       </c>
       <c r="D38" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E38" s="19" t="inlineStr">
@@ -5292,51 +5292,51 @@
       </c>
       <c r="F38" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="G38" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="H38" s="30" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I38" s="30" t="n">
-        <v>43</v>
+        <v>86.7</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>7</v>
+        <v>13.3</v>
       </c>
       <c r="K38" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+      <c r="L38" s="31" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="M38" s="18" t="inlineStr">
         <is>
-          <t>**基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）**</t>
+          <t>―</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>回収票の点検・ナンバリング・データ入力</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="D39" s="19" t="inlineStr">
@@ -5346,27 +5346,27 @@
       </c>
       <c r="E39" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G39" s="20" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H39" s="30" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I39" s="30" t="n">
-        <v>86.7</v>
+        <v>75</v>
       </c>
       <c r="J39" s="30" t="n">
-        <v>13.3</v>
+        <v>15</v>
       </c>
       <c r="K39" s="19" t="n">
         <v>3</v>
@@ -5378,24 +5378,24 @@
       </c>
       <c r="M39" s="18" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
         </is>
       </c>
       <c r="D40" s="19" t="inlineStr">
@@ -5405,12 +5405,12 @@
       </c>
       <c r="E40" s="19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F40" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G40" s="22" t="inlineStr">
@@ -5419,16 +5419,16 @@
         </is>
       </c>
       <c r="H40" s="30" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="I40" s="30" t="n">
-        <v>75</v>
+        <v>24.2</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L40" s="31" t="inlineStr">
         <is>
@@ -5437,24 +5437,24 @@
       </c>
       <c r="M40" s="18" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>**レビュー所見の反映（重大5件）、ヒアリング記録の完成**</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="D41" s="19" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="E41" s="19" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G41" s="22" t="inlineStr">
@@ -5478,16 +5478,16 @@
         </is>
       </c>
       <c r="H41" s="30" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I41" s="30" t="n">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>15.8</v>
+        <v>20</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L41" s="31" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="M41" s="18" t="inlineStr">
         <is>
-          <t>**レビュー所見の反映（重大5件）、ヒアリング記録の完成**</t>
+          <t>**イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要**</t>
         </is>
       </c>
     </row>
@@ -5916,17 +5916,17 @@
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>課題の抽出</t>
         </is>
       </c>
       <c r="D49" s="19" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G49" s="22" t="inlineStr">
@@ -5959,7 +5959,7 @@
         <v>75</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L49" s="31" t="inlineStr">
         <is>
@@ -5968,24 +5968,24 @@
       </c>
       <c r="M49" s="18" t="inlineStr">
         <is>
-          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
+          <t>調査結果・ヒアリング結果</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>課題の抽出</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="D50" s="19" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="E50" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="F50" s="19" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G50" s="22" t="inlineStr">
@@ -6009,16 +6009,16 @@
         </is>
       </c>
       <c r="H50" s="30" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I50" s="30" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L50" s="31" t="inlineStr">
         <is>
@@ -6027,14 +6027,14 @@
       </c>
       <c r="M50" s="18" t="inlineStr">
         <is>
-          <t>調査結果・ヒアリング結果</t>
+          <t>**条件なしで着手できる。調査結果を待たずに構成・本文は書ける**</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 65.0％　対　予定進捗率 62.8％　乖離 +2.2ポイント</t>
+          <t>加重の実績進捗率 65.7％　対　予定進捗率 62.8％　乖離 +2.9ポイント</t>
         </is>
       </c>
     </row>
@@ -6055,14 +6055,14 @@
     <row r="55">
       <c r="A55" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　おおむね予定どおり 28件</t>
+          <t xml:space="preserve">　おおむね予定どおり 27件</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="33" t="inlineStr">
         <is>
-          <t xml:space="preserve">　前倒し 12件</t>
+          <t xml:space="preserve">　前倒し 13件</t>
         </is>
       </c>
     </row>
@@ -9112,14 +9112,14 @@
         </is>
       </c>
       <c r="L41" s="21" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="M41" s="22" t="n">
         <v>5</v>
       </c>
       <c r="N41" s="18" t="inlineStr">
         <is>
-          <t>**10月23日、仕様書22条項の網羅性（充足9・一部9・不足1・前提3）と図表37項目を点検した。不足は調査結果の図（土台の第2部は令和5年度調査）、施策体系図、障害支援区分の表、ヒアリング結果、イラストの割付。図表の番号・題名・資料・数字・用語の統一規則を高齢者計画にそろえる。****第4版（令和8年10月21日・45頁）。調査結果と見込量の数値を本文に入れた。未確定90箇所。****素案 第1版を作成（03_計画素案・31頁・表25・見出し30）。**骨子案 第3版の構成を本文に展開し、第1部総論（3章）・第2部分野別施策（10章38節）・第3部成果目標と見込量・第4部計画の推進までを置いた。**両計画の接点の節は ono_setten から引き、高齢者計画と同じ文言。****成果目標の値とサービス見込量は町データ待ち**</t>
+          <t>**10月23日、図表の点検の作業1〜7を実施。令和8年度調査の図19点を作成し、他メンバー素案（変更履歴付き 第2弾）の第2部の前回調査の表を置き換え、図表の通し番号・題名・資料、「障害」「障がい」の書き分け（前回計画の規則）、数字の半角をそろえた。当方素案は第5版（53頁）とし、協議用の見出し・表は町との協議資料に移した。**10月23日、仕様書22条項の網羅性（充足9・一部9・不足1・前提3）と図表37項目を点検した。**第4版（令和8年10月21日・45頁）。調査結果と見込量の数値を本文に入れた。未確定90箇所。****素案 第1版を作成（03_計画素案・31頁・表25・見出し30）。**骨子案 第3版の構成を本文に展開し、第1部総論（3章）・第2部分野別施策（10章38節）・第3部成果目標と見込量・第4部計画の推進までを置いた。**両計画の接点の節は ono_setten から引き、高齢者計画と同じ文言。****成果目標の値とサービス見込量は町データ待ち**</t>
         </is>
       </c>
       <c r="O41" s="18" t="inlineStr">
@@ -9619,20 +9619,20 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="K48" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K48" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L48" s="21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="M48" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N48" s="18" t="inlineStr">
         <is>
-          <t>**10月23日、図表を前回計画・他団体の案件・土台・当方の4本で点検し、イラスト起こしの候補5点を挙げた（12_進捗管理「仕様書の網羅性確認と図表の点検」）。**</t>
+          <t>**10月23日、イラスト起こしの候補5点の割付とラフを作成した（10_納品・印刷「イラスト起こしの割付案」）。町と4点程度を選ぶ。施策体系図は基本理念・基本目標の設定後。**</t>
         </is>
       </c>
       <c r="O48" s="18" t="inlineStr">

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261023.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_業務進捗管理表_障がい_20261023.xlsx
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.6566115702479338</v>
+        <v>0.6599173553719008</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>0.02871074380165282</v>
+        <v>0.03201652892561981</v>
       </c>
     </row>
     <row r="8">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>3-3</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>依頼の送付・日程調整</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="F2" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G2" s="25" t="inlineStr">
@@ -3180,81 +3180,81 @@
         <v>0</v>
       </c>
       <c r="I2" s="30" t="n">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="J2" s="30" t="n">
-        <v>-100</v>
+        <v>-86.7</v>
       </c>
       <c r="K2" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="23" t="inlineStr">
-        <is>
-          <t>期限超過（1か月）</t>
+        <v>4</v>
+      </c>
+      <c r="L2" s="24" t="inlineStr">
+        <is>
+          <t>遅れ</t>
         </is>
       </c>
       <c r="M2" s="18" t="inlineStr">
         <is>
-          <t>対象先の選定</t>
+          <t>日程調整</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="18" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="B3" s="19" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>町データの受領</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="G3" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H3" s="30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I3" s="30" t="n">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="J3" s="30" t="n">
-        <v>-86.7</v>
+        <v>-60</v>
       </c>
       <c r="K3" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="L3" s="24" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t>期限超過（1か月）</t>
         </is>
       </c>
       <c r="M3" s="18" t="inlineStr">
         <is>
-          <t>日程調整</t>
+          <t>**町の回答。P2・P5・P6が依存する**</t>
         </is>
       </c>
     </row>
@@ -3266,17 +3266,17 @@
       </c>
       <c r="B4" s="19" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>1-7</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>町データの受領</t>
+          <t>工程変更の協議と打合せ記録の作成</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="E4" s="19" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="F4" s="19" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="G4" s="22" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="H4" s="30" t="n">
@@ -3304,53 +3304,53 @@
         <v>-60</v>
       </c>
       <c r="K4" s="19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L4" s="23" t="inlineStr">
         <is>
-          <t>期限超過（1か月）</t>
+          <t>期限超過（2か月）</t>
         </is>
       </c>
       <c r="M4" s="18" t="inlineStr">
         <is>
-          <t>**町の回答。P2・P5・P6が依存する**</t>
+          <t>**町との協議。8月19日の協議会またはその前後に行う**</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
         <is>
-          <t>1-7</t>
+          <t>3-3</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>工程変更の協議と打合せ記録の作成</t>
+          <t>依頼の送付・日程調整</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F5" s="19" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="H5" s="30" t="n">
@@ -3363,16 +3363,16 @@
         <v>-60</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L5" s="23" t="inlineStr">
         <is>
-          <t>期限超過（2か月）</t>
+          <t>期限超過（1か月）</t>
         </is>
       </c>
       <c r="M5" s="18" t="inlineStr">
         <is>
-          <t>**町との協議。8月19日の協議会またはその前後に行う**</t>
+          <t>対象先の選定</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
     <row r="52">
       <c r="A52" s="32" t="inlineStr">
         <is>
-          <t>加重の実績進捗率 65.7％　対　予定進捗率 62.8％　乖離 +2.9ポイント</t>
+          <t>加重の実績進捗率 66.0％　対　予定進捗率 62.8％　乖離 +3.2ポイント</t>
         </is>
       </c>
     </row>
@@ -8083,20 +8083,20 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="K27" s="25" t="inlineStr">
-        <is>
-          <t>未着手</t>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="L27" s="21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M27" s="22" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="18" t="inlineStr">
         <is>
-          <t>**ヒアリングシートは作成済み。依頼文の名義と送付方法を町に確認中。11月上旬に送付予定。**依頼文の記載事項は実施計画書に整理</t>
+          <t>**10月23日、依頼文一式（町長名版・受託者名版。依頼文・日程調整票・計画の概要・個人情報の取扱い）と送付・日程管理表を作成した（15_ヒアリング・調査設計）。名義・同席・町外の対象先を町に確認し、11月4日（水）頃送付、返信11月10日（火）、実施11月12日（木）〜20日（金）。**依頼文の記載事項は実施計画書に整理</t>
         </is>
       </c>
       <c r="O27" s="18" t="inlineStr">
